--- a/Service_Watch_Test/Nebula_Galaxy_sw_requirements_v7.xlsx
+++ b/Service_Watch_Test/Nebula_Galaxy_sw_requirements_v7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u217617\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\Service_Watch_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C146F4B8-E658-4A29-93EF-DEEAA6224FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FEC448-1886-442F-858C-06E143EBF8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="767" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="0" windowWidth="16005" windowHeight="18210" tabRatio="767" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ServiceWatch Log Parameters" sheetId="15" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Name Changes'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'New SPNs'!$A$2:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ServiceWatch Log Parameters'!$A$1:$O$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ServiceWatch Log Parameters'!$A$1:$P$165</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2116,7 +2116,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3157,7 +3157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:PX165"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" customWidth="1"/>
@@ -3178,7 +3178,7 @@
     <col min="17" max="17" width="91.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:440" s="1" customFormat="1" ht="25.9" customHeight="1">
+    <row r="1" spans="1:440" s="1" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:440" s="8" customFormat="1">
+    <row r="2" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>16</v>
       </c>
@@ -3696,7 +3696,7 @@
       <c r="PW2"/>
       <c r="PX2"/>
     </row>
-    <row r="3" spans="1:440" s="8" customFormat="1">
+    <row r="3" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>24</v>
       </c>
@@ -4164,7 +4164,7 @@
       <c r="PW3"/>
       <c r="PX3"/>
     </row>
-    <row r="4" spans="1:440" s="8" customFormat="1">
+    <row r="4" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>26</v>
       </c>
@@ -4634,7 +4634,7 @@
       <c r="PW4"/>
       <c r="PX4"/>
     </row>
-    <row r="5" spans="1:440" s="8" customFormat="1">
+    <row r="5" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>30</v>
       </c>
@@ -5104,7 +5104,7 @@
       <c r="PW5"/>
       <c r="PX5"/>
     </row>
-    <row r="6" spans="1:440" s="8" customFormat="1">
+    <row r="6" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>36</v>
       </c>
@@ -5574,7 +5574,7 @@
       <c r="PW6"/>
       <c r="PX6"/>
     </row>
-    <row r="7" spans="1:440" s="8" customFormat="1">
+    <row r="7" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>39</v>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="PW7"/>
       <c r="PX7"/>
     </row>
-    <row r="8" spans="1:440" s="8" customFormat="1">
+    <row r="8" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>40</v>
       </c>
@@ -6514,7 +6514,7 @@
       <c r="PW8"/>
       <c r="PX8"/>
     </row>
-    <row r="9" spans="1:440" s="8" customFormat="1">
+    <row r="9" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>44</v>
       </c>
@@ -6984,7 +6984,7 @@
       <c r="PW9"/>
       <c r="PX9"/>
     </row>
-    <row r="10" spans="1:440" s="8" customFormat="1">
+    <row r="10" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>48</v>
       </c>
@@ -7454,7 +7454,7 @@
       <c r="PW10"/>
       <c r="PX10"/>
     </row>
-    <row r="11" spans="1:440" s="8" customFormat="1">
+    <row r="11" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>49</v>
       </c>
@@ -7924,7 +7924,7 @@
       <c r="PW11"/>
       <c r="PX11"/>
     </row>
-    <row r="12" spans="1:440" s="8" customFormat="1">
+    <row r="12" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>52</v>
       </c>
@@ -8394,7 +8394,7 @@
       <c r="PW12"/>
       <c r="PX12"/>
     </row>
-    <row r="13" spans="1:440" s="8" customFormat="1">
+    <row r="13" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>56</v>
       </c>
@@ -8864,7 +8864,7 @@
       <c r="PW13"/>
       <c r="PX13"/>
     </row>
-    <row r="14" spans="1:440" s="8" customFormat="1">
+    <row r="14" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>57</v>
       </c>
@@ -9334,7 +9334,7 @@
       <c r="PW14"/>
       <c r="PX14"/>
     </row>
-    <row r="15" spans="1:440" s="8" customFormat="1">
+    <row r="15" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>60</v>
       </c>
@@ -9806,7 +9806,7 @@
       <c r="PW15"/>
       <c r="PX15"/>
     </row>
-    <row r="16" spans="1:440" s="8" customFormat="1">
+    <row r="16" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>64</v>
       </c>
@@ -10276,7 +10276,7 @@
       <c r="PW16"/>
       <c r="PX16"/>
     </row>
-    <row r="17" spans="1:440">
+    <row r="17" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>68</v>
       </c>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="P17" s="12"/>
     </row>
-    <row r="18" spans="1:440">
+    <row r="18" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>71</v>
       </c>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P18" s="12"/>
     </row>
-    <row r="19" spans="1:440">
+    <row r="19" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>76</v>
       </c>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="12"/>
     </row>
-    <row r="20" spans="1:440">
+    <row r="20" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>79</v>
       </c>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="P20" s="12"/>
     </row>
-    <row r="21" spans="1:440">
+    <row r="21" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>82</v>
       </c>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="P21" s="12"/>
     </row>
-    <row r="22" spans="1:440" s="8" customFormat="1">
+    <row r="22" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>85</v>
       </c>
@@ -10966,7 +10966,7 @@
       <c r="PW22"/>
       <c r="PX22"/>
     </row>
-    <row r="23" spans="1:440">
+    <row r="23" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>90</v>
       </c>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="P23" s="12"/>
     </row>
-    <row r="24" spans="1:440">
+    <row r="24" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>93</v>
       </c>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="P24" s="12"/>
     </row>
-    <row r="25" spans="1:440" s="8" customFormat="1">
+    <row r="25" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>96</v>
       </c>
@@ -11522,7 +11522,7 @@
       <c r="PW25"/>
       <c r="PX25"/>
     </row>
-    <row r="26" spans="1:440">
+    <row r="26" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="P26" s="12"/>
     </row>
-    <row r="27" spans="1:440">
+    <row r="27" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>103</v>
       </c>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="P27" s="12"/>
     </row>
-    <row r="28" spans="1:440">
+    <row r="28" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>104</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:440" s="8" customFormat="1">
+    <row r="29" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>108</v>
       </c>
@@ -12120,7 +12120,7 @@
       <c r="PW29"/>
       <c r="PX29"/>
     </row>
-    <row r="30" spans="1:440">
+    <row r="30" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>111</v>
       </c>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P30" s="12"/>
     </row>
-    <row r="31" spans="1:440" s="8" customFormat="1">
+    <row r="31" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>116</v>
       </c>
@@ -12638,7 +12638,7 @@
       <c r="PW31"/>
       <c r="PX31"/>
     </row>
-    <row r="32" spans="1:440" s="8" customFormat="1">
+    <row r="32" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>121</v>
       </c>
@@ -13110,7 +13110,7 @@
       <c r="PW32"/>
       <c r="PX32"/>
     </row>
-    <row r="33" spans="1:440" s="8" customFormat="1">
+    <row r="33" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>122</v>
       </c>
@@ -13582,7 +13582,7 @@
       <c r="PW33"/>
       <c r="PX33"/>
     </row>
-    <row r="34" spans="1:440" s="8" customFormat="1">
+    <row r="34" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
         <v>126</v>
       </c>
@@ -14052,7 +14052,7 @@
       <c r="PW34"/>
       <c r="PX34"/>
     </row>
-    <row r="35" spans="1:440" s="8" customFormat="1">
+    <row r="35" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
         <v>131</v>
       </c>
@@ -14522,7 +14522,7 @@
       <c r="PW35"/>
       <c r="PX35"/>
     </row>
-    <row r="36" spans="1:440" s="8" customFormat="1">
+    <row r="36" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>134</v>
       </c>
@@ -14992,7 +14992,7 @@
       <c r="PW36"/>
       <c r="PX36"/>
     </row>
-    <row r="37" spans="1:440">
+    <row r="37" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>138</v>
       </c>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="P37" s="12"/>
     </row>
-    <row r="38" spans="1:440">
+    <row r="38" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>141</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:440">
+    <row r="39" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>145</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:440">
+    <row r="40" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>149</v>
       </c>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P40" s="12"/>
     </row>
-    <row r="41" spans="1:440">
+    <row r="41" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>151</v>
       </c>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="P41" s="12"/>
     </row>
-    <row r="42" spans="1:440">
+    <row r="42" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>155</v>
       </c>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="P42" s="12"/>
     </row>
-    <row r="43" spans="1:440">
+    <row r="43" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>158</v>
       </c>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="P43" s="12"/>
     </row>
-    <row r="44" spans="1:440">
+    <row r="44" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>161</v>
       </c>
@@ -15352,7 +15352,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="45" spans="1:440">
+    <row r="45" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>165</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:440">
+    <row r="46" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>170</v>
       </c>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="P46" s="12"/>
     </row>
-    <row r="47" spans="1:440">
+    <row r="47" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>172</v>
       </c>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="P47" s="12"/>
     </row>
-    <row r="48" spans="1:440">
+    <row r="48" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>174</v>
       </c>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="P48" s="12"/>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>177</v>
       </c>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="P49" s="12"/>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>179</v>
       </c>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="P50" s="12"/>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>182</v>
       </c>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="P51" s="12"/>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>187</v>
       </c>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="P52" s="12"/>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>190</v>
       </c>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="P53" s="12"/>
     </row>
-    <row r="54" spans="1:16" s="3" customFormat="1">
+    <row r="54" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
         <v>193</v>
       </c>
@@ -15798,7 +15798,7 @@
       </c>
       <c r="P54" s="34"/>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>196</v>
       </c>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="P55" s="12"/>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>199</v>
       </c>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="P56" s="12"/>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>202</v>
       </c>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="P57" s="12"/>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>207</v>
       </c>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="P58" s="12"/>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>210</v>
       </c>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="P59" s="12"/>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>213</v>
       </c>
@@ -16072,7 +16072,7 @@
       </c>
       <c r="P60" s="12"/>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>216</v>
       </c>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="P61" s="12"/>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>219</v>
       </c>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="P62" s="12"/>
     </row>
-    <row r="63" spans="1:16" s="3" customFormat="1">
+    <row r="63" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
         <v>223</v>
       </c>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="P63" s="34"/>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>226</v>
       </c>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="P64" s="12"/>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>229</v>
       </c>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="P65" s="12"/>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>232</v>
       </c>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="P66" s="12"/>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>236</v>
       </c>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="P67" s="12"/>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>239</v>
       </c>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P68" s="12"/>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>242</v>
       </c>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="P69" s="12"/>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>245</v>
       </c>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="P70" s="12"/>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>248</v>
       </c>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="P71" s="12"/>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>251</v>
       </c>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="P72" s="12"/>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>255</v>
       </c>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="P73" s="12"/>
     </row>
-    <row r="74" spans="1:16" s="3" customFormat="1">
+    <row r="74" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
         <v>259</v>
       </c>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="P74" s="34"/>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>263</v>
       </c>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="P75" s="12"/>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>266</v>
       </c>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="P76" s="12"/>
     </row>
-    <row r="77" spans="1:16" s="3" customFormat="1">
+    <row r="77" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
         <v>269</v>
       </c>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="P77" s="34"/>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>272</v>
       </c>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="P78" s="12"/>
     </row>
-    <row r="79" spans="1:16" s="3" customFormat="1">
+    <row r="79" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
         <v>275</v>
       </c>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="P79" s="34"/>
     </row>
-    <row r="80" spans="1:16" s="3" customFormat="1">
+    <row r="80" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
         <v>278</v>
       </c>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P80" s="34"/>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>281</v>
       </c>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="P81" s="12"/>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>284</v>
       </c>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="P82" s="12"/>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>287</v>
       </c>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="P83" s="12"/>
     </row>
-    <row r="84" spans="1:16" s="3" customFormat="1">
+    <row r="84" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
         <v>290</v>
       </c>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="P84" s="34"/>
     </row>
-    <row r="85" spans="1:16" s="3" customFormat="1">
+    <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
         <v>293</v>
       </c>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="P85" s="34"/>
     </row>
-    <row r="86" spans="1:16" s="3" customFormat="1">
+    <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
         <v>297</v>
       </c>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="P86" s="34"/>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
         <v>301</v>
       </c>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="P87" s="12"/>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>304</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>308</v>
       </c>
@@ -17366,7 +17366,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:16" s="3" customFormat="1">
+    <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="34" t="s">
         <v>312</v>
       </c>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="P90" s="37"/>
     </row>
-    <row r="91" spans="1:16" s="3" customFormat="1">
+    <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="34" t="s">
         <v>315</v>
       </c>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="P91" s="37"/>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>318</v>
       </c>
@@ -17500,7 +17500,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>322</v>
       </c>
@@ -17548,7 +17548,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>327</v>
       </c>
@@ -17596,7 +17596,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>331</v>
       </c>
@@ -17644,7 +17644,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>335</v>
       </c>
@@ -17690,7 +17690,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>339</v>
       </c>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="P97" s="12"/>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
         <v>342</v>
       </c>
@@ -17782,7 +17782,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>346</v>
       </c>
@@ -17828,7 +17828,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>350</v>
       </c>
@@ -17876,7 +17876,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
         <v>354</v>
       </c>
@@ -17922,7 +17922,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
         <v>358</v>
       </c>
@@ -17968,7 +17968,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>362</v>
       </c>
@@ -18014,7 +18014,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
         <v>366</v>
       </c>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="P104" s="12"/>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
         <v>369</v>
       </c>
@@ -18104,7 +18104,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="106" spans="1:16" s="3" customFormat="1" ht="29.1">
+    <row r="106" spans="1:16" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
         <v>373</v>
       </c>
@@ -18148,7 +18148,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="14.25" customHeight="1">
+    <row r="107" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
         <v>377</v>
       </c>
@@ -18194,7 +18194,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
         <v>381</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>385</v>
       </c>
@@ -18288,7 +18288,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
         <v>389</v>
       </c>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="P110" s="12"/>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
         <v>392</v>
       </c>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="P111" s="12"/>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
         <v>395</v>
       </c>
@@ -18412,7 +18412,7 @@
       </c>
       <c r="P112" s="12"/>
     </row>
-    <row r="113" spans="1:440">
+    <row r="113" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
         <v>399</v>
       </c>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="P113" s="12"/>
     </row>
-    <row r="114" spans="1:440">
+    <row r="114" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
         <v>400</v>
       </c>
@@ -18476,7 +18476,7 @@
       </c>
       <c r="P114" s="12"/>
     </row>
-    <row r="115" spans="1:440">
+    <row r="115" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
         <v>401</v>
       </c>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="P115" s="12"/>
     </row>
-    <row r="116" spans="1:440">
+    <row r="116" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
         <v>404</v>
       </c>
@@ -18562,7 +18562,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="117" spans="1:440">
+    <row r="117" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>408</v>
       </c>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="P117" s="12"/>
     </row>
-    <row r="118" spans="1:440">
+    <row r="118" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
         <v>411</v>
       </c>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="P118" s="12"/>
     </row>
-    <row r="119" spans="1:440">
+    <row r="119" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>414</v>
       </c>
@@ -18696,7 +18696,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="120" spans="1:440">
+    <row r="120" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
         <v>418</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="121" spans="1:440">
+    <row r="121" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>421</v>
       </c>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="P121" s="12"/>
     </row>
-    <row r="122" spans="1:440">
+    <row r="122" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
         <v>424</v>
       </c>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="P122" s="12"/>
     </row>
-    <row r="123" spans="1:440">
+    <row r="123" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>427</v>
       </c>
@@ -18874,7 +18874,7 @@
       </c>
       <c r="P123" s="12"/>
     </row>
-    <row r="124" spans="1:440">
+    <row r="124" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
         <v>430</v>
       </c>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="P124" s="12"/>
     </row>
-    <row r="125" spans="1:440">
+    <row r="125" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
         <v>433</v>
       </c>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P125" s="12"/>
     </row>
-    <row r="126" spans="1:440" s="8" customFormat="1">
+    <row r="126" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="22" t="s">
         <v>436</v>
       </c>
@@ -19428,7 +19428,7 @@
       <c r="PW126"/>
       <c r="PX126"/>
     </row>
-    <row r="127" spans="1:440">
+    <row r="127" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
         <v>440</v>
       </c>
@@ -19472,7 +19472,7 @@
       </c>
       <c r="P127" s="12"/>
     </row>
-    <row r="128" spans="1:440">
+    <row r="128" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
         <v>443</v>
       </c>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="P128" s="12"/>
     </row>
-    <row r="129" spans="1:440">
+    <row r="129" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>446</v>
       </c>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="P129" s="12"/>
     </row>
-    <row r="130" spans="1:440">
+    <row r="130" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
         <v>449</v>
       </c>
@@ -19600,7 +19600,7 @@
       </c>
       <c r="P130" s="12"/>
     </row>
-    <row r="131" spans="1:440">
+    <row r="131" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
         <v>452</v>
       </c>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="P131" s="12"/>
     </row>
-    <row r="132" spans="1:440">
+    <row r="132" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
         <v>455</v>
       </c>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P132" s="12"/>
     </row>
-    <row r="133" spans="1:440">
+    <row r="133" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
         <v>458</v>
       </c>
@@ -19726,7 +19726,7 @@
       </c>
       <c r="P133" s="12"/>
     </row>
-    <row r="134" spans="1:440">
+    <row r="134" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
         <v>461</v>
       </c>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="P134" s="12"/>
     </row>
-    <row r="135" spans="1:440">
+    <row r="135" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
         <v>462</v>
       </c>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="P135" s="12"/>
     </row>
-    <row r="136" spans="1:440">
+    <row r="136" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
         <v>465</v>
       </c>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P136" s="12"/>
     </row>
-    <row r="137" spans="1:440">
+    <row r="137" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>469</v>
       </c>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="P137" s="12"/>
     </row>
-    <row r="138" spans="1:440" s="6" customFormat="1">
+    <row r="138" spans="1:440" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="39" t="s">
         <v>470</v>
       </c>
@@ -20362,7 +20362,7 @@
       <c r="PW138"/>
       <c r="PX138"/>
     </row>
-    <row r="139" spans="1:440">
+    <row r="139" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
         <v>471</v>
       </c>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="P139" s="12"/>
     </row>
-    <row r="140" spans="1:440">
+    <row r="140" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
         <v>474</v>
       </c>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="P140" s="12"/>
     </row>
-    <row r="141" spans="1:440" s="6" customFormat="1">
+    <row r="141" spans="1:440" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="39" t="s">
         <v>475</v>
       </c>
@@ -20916,7 +20916,7 @@
       <c r="PW141"/>
       <c r="PX141"/>
     </row>
-    <row r="142" spans="1:440">
+    <row r="142" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
         <v>478</v>
       </c>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="P142" s="12"/>
     </row>
-    <row r="143" spans="1:440">
+    <row r="143" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
         <v>481</v>
       </c>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="P143" s="12"/>
     </row>
-    <row r="144" spans="1:440" s="6" customFormat="1">
+    <row r="144" spans="1:440" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="40" t="s">
         <v>482</v>
       </c>
@@ -21466,7 +21466,7 @@
       <c r="PW144"/>
       <c r="PX144"/>
     </row>
-    <row r="145" spans="1:440">
+    <row r="145" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>485</v>
       </c>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="P145" s="12"/>
     </row>
-    <row r="146" spans="1:440">
+    <row r="146" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
         <v>488</v>
       </c>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="P146" s="12"/>
     </row>
-    <row r="147" spans="1:440" s="8" customFormat="1">
+    <row r="147" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="22" t="s">
         <v>491</v>
       </c>
@@ -22018,7 +22018,7 @@
       <c r="PW147"/>
       <c r="PX147"/>
     </row>
-    <row r="148" spans="1:440">
+    <row r="148" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
         <v>494</v>
       </c>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="P148" s="12"/>
     </row>
-    <row r="149" spans="1:440" s="2" customFormat="1">
+    <row r="149" spans="1:440" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="44" t="s">
         <v>498</v>
       </c>
@@ -22100,7 +22100,7 @@
       </c>
       <c r="P149" s="47"/>
     </row>
-    <row r="150" spans="1:440" s="2" customFormat="1">
+    <row r="150" spans="1:440" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="44" t="s">
         <v>501</v>
       </c>
@@ -22140,7 +22140,7 @@
       </c>
       <c r="P150" s="47"/>
     </row>
-    <row r="151" spans="1:440">
+    <row r="151" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
         <v>504</v>
       </c>
@@ -22182,7 +22182,7 @@
       </c>
       <c r="P151" s="12"/>
     </row>
-    <row r="152" spans="1:440">
+    <row r="152" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
         <v>507</v>
       </c>
@@ -22224,7 +22224,7 @@
       </c>
       <c r="P152" s="12"/>
     </row>
-    <row r="153" spans="1:440" s="8" customFormat="1">
+    <row r="153" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="22" t="s">
         <v>510</v>
       </c>
@@ -22686,7 +22686,7 @@
       <c r="PW153"/>
       <c r="PX153"/>
     </row>
-    <row r="154" spans="1:440" s="8" customFormat="1">
+    <row r="154" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="22" t="s">
         <v>515</v>
       </c>
@@ -23148,7 +23148,7 @@
       <c r="PW154"/>
       <c r="PX154"/>
     </row>
-    <row r="155" spans="1:440" s="8" customFormat="1">
+    <row r="155" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="22" t="s">
         <v>518</v>
       </c>
@@ -23610,7 +23610,7 @@
       <c r="PW155"/>
       <c r="PX155"/>
     </row>
-    <row r="156" spans="1:440" s="8" customFormat="1">
+    <row r="156" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="22" t="s">
         <v>521</v>
       </c>
@@ -24072,7 +24072,7 @@
       <c r="PW156"/>
       <c r="PX156"/>
     </row>
-    <row r="157" spans="1:440" s="8" customFormat="1">
+    <row r="157" spans="1:440" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="22" t="s">
         <v>524</v>
       </c>
@@ -24538,7 +24538,7 @@
       <c r="PW157"/>
       <c r="PX157"/>
     </row>
-    <row r="158" spans="1:440">
+    <row r="158" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
         <v>527</v>
       </c>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="P158" s="12"/>
     </row>
-    <row r="159" spans="1:440">
+    <row r="159" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>530</v>
       </c>
@@ -24622,7 +24622,7 @@
       </c>
       <c r="P159" s="12"/>
     </row>
-    <row r="160" spans="1:440">
+    <row r="160" spans="1:440" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
         <v>533</v>
       </c>
@@ -24664,7 +24664,7 @@
       </c>
       <c r="P160" s="12"/>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
         <v>536</v>
       </c>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="P161" s="12"/>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
         <v>539</v>
       </c>
@@ -24748,7 +24748,7 @@
       </c>
       <c r="P162" s="12"/>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
         <v>543</v>
       </c>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="P163" s="12"/>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
         <v>545</v>
       </c>
@@ -24836,7 +24836,7 @@
       </c>
       <c r="P164" s="12"/>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
         <v>549</v>
       </c>
@@ -24879,7 +24879,7 @@
       <c r="P165" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O165" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <autoFilter ref="A1:P165" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:L148">
     <sortCondition ref="C2:C148"/>
   </sortState>
@@ -24892,13 +24892,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD8766CB-2EEB-4E96-B184-17CA6C359AC6}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="15" customFormat="1">
+    <row r="1" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
         <v>2</v>
       </c>
@@ -24909,7 +24909,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>382</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>386</v>
       </c>
@@ -24931,7 +24931,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>65</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>444</v>
       </c>
@@ -24953,7 +24953,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>294</v>
       </c>
@@ -24964,7 +24964,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>298</v>
       </c>
@@ -24975,7 +24975,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>302</v>
       </c>
@@ -24986,7 +24986,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>374</v>
       </c>
@@ -24997,7 +24997,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>405</v>
       </c>
@@ -25008,7 +25008,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>175</v>
       </c>
@@ -25019,7 +25019,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>162</v>
       </c>
@@ -25030,7 +25030,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>166</v>
       </c>
@@ -25041,7 +25041,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>288</v>
       </c>
@@ -25052,7 +25052,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>194</v>
       </c>
@@ -25063,7 +25063,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>291</v>
       </c>
@@ -25074,7 +25074,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>276</v>
       </c>
@@ -25085,7 +25085,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>279</v>
       </c>
@@ -25096,7 +25096,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>270</v>
       </c>
@@ -25107,7 +25107,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
@@ -25118,7 +25118,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>298</v>
       </c>
@@ -25129,7 +25129,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="51" t="s">
         <v>302</v>
       </c>
@@ -25140,7 +25140,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="51" t="s">
         <v>305</v>
       </c>
@@ -25151,7 +25151,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>309</v>
       </c>
@@ -25162,7 +25162,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>313</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>316</v>
       </c>
@@ -25184,7 +25184,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>367</v>
       </c>
@@ -25195,7 +25195,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>319</v>
       </c>
@@ -25206,7 +25206,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>323</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>328</v>
       </c>
@@ -25228,7 +25228,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>332</v>
       </c>
@@ -25239,7 +25239,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>336</v>
       </c>
@@ -25250,7 +25250,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>340</v>
       </c>
@@ -25261,7 +25261,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>343</v>
       </c>
@@ -25272,7 +25272,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>347</v>
       </c>
@@ -25283,7 +25283,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>351</v>
       </c>
@@ -25294,7 +25294,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>355</v>
       </c>
@@ -25305,7 +25305,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="51" t="s">
         <v>359</v>
       </c>
@@ -25316,7 +25316,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="51" t="s">
         <v>363</v>
       </c>
@@ -25327,7 +25327,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
         <v>370</v>
       </c>
@@ -25338,7 +25338,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="52" t="s">
         <v>374</v>
       </c>
@@ -25349,7 +25349,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="51" t="s">
         <v>378</v>
       </c>
@@ -25360,7 +25360,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
         <v>382</v>
       </c>
@@ -25371,7 +25371,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="51" t="s">
         <v>386</v>
       </c>
@@ -25382,7 +25382,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="51" t="s">
         <v>390</v>
       </c>
@@ -25393,7 +25393,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="51" t="s">
         <v>393</v>
       </c>
@@ -25445,13 +25445,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53C17B0-2C90-4657-87D0-885BD1C76F40}">
   <dimension ref="A2:B4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>595</v>
       </c>
@@ -25459,12 +25459,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>597</v>
       </c>
@@ -25477,20 +25477,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EED15DE-F074-4067-9383-D60833625C8F}">
   <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="106.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="65" t="s">
         <v>598</v>
       </c>
       <c r="B1" s="65"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>599</v>
       </c>
@@ -25498,7 +25498,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.95" customHeight="1">
+    <row r="3" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -25506,7 +25506,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.600000000000001" customHeight="1">
+    <row r="4" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -25514,7 +25514,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.95" customHeight="1">
+    <row r="5" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -25522,7 +25522,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.95" customHeight="1">
+    <row r="6" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -25530,7 +25530,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.95" customHeight="1">
+    <row r="7" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -25539,7 +25539,7 @@
       </c>
       <c r="E7" s="7"/>
     </row>
-    <row r="8" spans="1:5" ht="18.95" customHeight="1">
+    <row r="8" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -25547,13 +25547,13 @@
         <v>606</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="65" t="s">
         <v>607</v>
       </c>
       <c r="B9" s="65"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>599</v>
       </c>
@@ -25561,7 +25561,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.95" customHeight="1">
+    <row r="11" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60">
         <v>1</v>
       </c>
@@ -25569,7 +25569,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18.600000000000001" customHeight="1">
+    <row r="12" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="58">
         <v>2</v>
       </c>
@@ -25577,7 +25577,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18.95" customHeight="1">
+    <row r="13" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>3</v>
       </c>
@@ -25585,7 +25585,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18.95" customHeight="1">
+    <row r="14" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61">
         <v>4</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18.95" customHeight="1">
+    <row r="15" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="61">
         <v>5</v>
       </c>
@@ -25602,7 +25602,7 @@
       </c>
       <c r="E15" s="7"/>
     </row>
-    <row r="16" spans="1:5" ht="18.95" customHeight="1">
+    <row r="16" spans="1:5" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="58">
         <v>6</v>
       </c>
@@ -25610,7 +25610,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="58">
         <v>7</v>
       </c>
@@ -25618,7 +25618,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="58">
         <v>8</v>
       </c>
@@ -25626,7 +25626,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>9</v>
       </c>
@@ -25634,7 +25634,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>10</v>
       </c>
@@ -25642,7 +25642,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="58">
         <v>11</v>
       </c>
@@ -25650,7 +25650,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
         <v>12</v>
       </c>
@@ -25658,7 +25658,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="58">
         <v>13</v>
       </c>
@@ -25666,7 +25666,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>14</v>
       </c>
@@ -25674,7 +25674,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="58">
         <v>15</v>
       </c>
@@ -25682,13 +25682,13 @@
         <v>622</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="64" t="s">
         <v>623</v>
       </c>
       <c r="B26" s="64"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="58">
         <v>1</v>
       </c>
@@ -25696,7 +25696,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="58">
         <v>2</v>
       </c>
@@ -25704,7 +25704,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="58">
         <v>3</v>
       </c>
@@ -25712,7 +25712,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="58">
         <v>4</v>
       </c>
@@ -25720,7 +25720,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
         <v>5</v>
       </c>
@@ -25728,7 +25728,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="58">
         <v>6</v>
       </c>
@@ -25736,19 +25736,19 @@
         <v>629</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>7</v>
       </c>
       <c r="B33" s="57"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="66" t="s">
         <v>630</v>
       </c>
       <c r="B34" s="66"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>1</v>
       </c>
@@ -25756,7 +25756,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>2</v>
       </c>
@@ -25764,13 +25764,13 @@
         <v>632</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="64" t="s">
         <v>633</v>
       </c>
       <c r="B37" s="64"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
         <v>1</v>
       </c>
@@ -25778,7 +25778,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>2</v>
       </c>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:7" ht="57.95">
+    <row r="40" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="58">
         <v>3</v>
       </c>
@@ -25795,7 +25795,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="58">
         <v>4</v>
       </c>
@@ -25803,7 +25803,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="58">
         <v>5</v>
       </c>
@@ -25811,7 +25811,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>6</v>
       </c>
@@ -25819,7 +25819,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="58">
         <v>7</v>
       </c>
@@ -25827,13 +25827,13 @@
         <v>640</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="64" t="s">
         <v>641</v>
       </c>
       <c r="B45" s="64"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="58">
         <v>1</v>
       </c>
@@ -25841,7 +25841,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="63" t="s">
         <v>643</v>
       </c>
@@ -25849,7 +25849,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="58">
         <v>1</v>
       </c>
@@ -25883,14 +25883,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E048DC5-22FE-476E-89FF-456C740296E6}">
   <dimension ref="A2:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="15.6">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
@@ -25899,7 +25899,7 @@
       </c>
       <c r="C2" s="13"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>139</v>
       </c>
@@ -25907,7 +25907,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>146</v>
       </c>
@@ -25926,13 +25926,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8408091-62CE-4962-BC46-5A7614973293}">
   <dimension ref="A2:B17"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>648</v>
       </c>
@@ -25940,7 +25940,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>650</v>
       </c>
@@ -25948,7 +25948,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>652</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>654</v>
       </c>
@@ -25964,7 +25964,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>656</v>
       </c>
@@ -25972,7 +25972,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>658</v>
       </c>
@@ -25980,7 +25980,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>660</v>
       </c>
@@ -25988,7 +25988,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>662</v>
       </c>
@@ -25996,7 +25996,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>664</v>
       </c>
@@ -26004,7 +26004,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>666</v>
       </c>
@@ -26012,7 +26012,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>668</v>
       </c>
@@ -26020,7 +26020,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>670</v>
       </c>
@@ -26028,7 +26028,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>672</v>
       </c>
@@ -26036,7 +26036,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>674</v>
       </c>
@@ -26044,7 +26044,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>676</v>
       </c>
@@ -26052,7 +26052,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>678</v>
       </c>
@@ -26296,15 +26296,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="7b1290c1-ec25-4ba7-abfb-f951834f7f49">
@@ -26357,14 +26348,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABDC2133-15B3-4EF8-A1C7-1270F517E3ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABDC2133-15B3-4EF8-A1C7-1270F517E3ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bd8c30b8-ab32-4db1-8113-9f553f3a72f5"/>
+    <ds:schemaRef ds:uri="7b1290c1-ec25-4ba7-abfb-f951834f7f49"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{180062D0-3542-4B34-BF0A-16630955B5EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A2B344F-70AE-4106-B3A2-1D0F1B8191FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b1290c1-ec25-4ba7-abfb-f951834f7f49"/>
+    <ds:schemaRef ds:uri="bd8c30b8-ab32-4db1-8113-9f553f3a72f5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A2B344F-70AE-4106-B3A2-1D0F1B8191FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{180062D0-3542-4B34-BF0A-16630955B5EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>